--- a/data/trans_orig/P1413-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1413-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de dolor de espalda en 2007</t>
+          <t>Población con diagnóstico de dolor de espalda, cuello, hombro, cintura (cervical/lumbar) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>239711</t>
+          <t>238185</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>295159</t>
+          <t>296320</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>356606</t>
+          <t>353518</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>419879</t>
+          <t>421110</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>610572</t>
+          <t>613174</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>697474</t>
+          <t>698151</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,75%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>736564</t>
+          <t>735403</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>792012</t>
+          <t>793538</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>895234</t>
+          <t>894003</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>958507</t>
+          <t>961595</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1649361</t>
+          <t>1648684</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1736263</t>
+          <t>1733661</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>73,87%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>176772</t>
+          <t>176466</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>230111</t>
+          <t>230255</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>186343</t>
+          <t>187482</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>241864</t>
+          <t>243022</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>379724</t>
+          <t>379565</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>454276</t>
+          <t>456087</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,9%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1463302</t>
+          <t>1463158</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1516641</t>
+          <t>1516947</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1345809</t>
+          <t>1344651</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1401330</t>
+          <t>1400191</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2826810</t>
+          <t>2824999</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2901362</t>
+          <t>2901521</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46454</t>
+          <t>46423</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77671</t>
+          <t>78519</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36911</t>
+          <t>36831</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64476</t>
+          <t>64787</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>91043</t>
+          <t>89823</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>130983</t>
+          <t>129134</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>473737</t>
+          <t>472889</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>504954</t>
+          <t>504985</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>411936</t>
+          <t>411625</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>439501</t>
+          <t>439581</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>896837</t>
+          <t>898686</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>936777</t>
+          <t>937997</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,26%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>485131</t>
+          <t>491205</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>571871</t>
+          <t>571470</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>604265</t>
+          <t>602194</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>696767</t>
+          <t>692257</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1109635</t>
+          <t>1123590</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1242998</t>
+          <t>1242838</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2704672</t>
+          <t>2705073</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2791412</t>
+          <t>2785338</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2682430</t>
+          <t>2686940</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2774932</t>
+          <t>2777003</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5412743</t>
+          <t>5412903</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5546106</t>
+          <t>5532151</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,12%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de dolor de espalda en 2012</t>
+          <t>Población con diagnóstico de dolor de espalda, cuello, hombro, cintura (cervical/lumbar) en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>130282</t>
+          <t>131539</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>178438</t>
+          <t>178781</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>326581</t>
+          <t>332010</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>395115</t>
+          <t>396574</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>471893</t>
+          <t>472309</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>555128</t>
+          <t>555141</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>796205</t>
+          <t>795862</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>844361</t>
+          <t>843104</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>942682</t>
+          <t>941223</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1011216</t>
+          <t>1005787</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1757312</t>
+          <t>1757299</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1840547</t>
+          <t>1840131</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,58%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>108289</t>
+          <t>113481</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>156835</t>
+          <t>157775</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>201810</t>
+          <t>206736</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>262769</t>
+          <t>267343</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>328999</t>
+          <t>329632</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>405553</t>
+          <t>405913</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1807122</t>
+          <t>1806182</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1855668</t>
+          <t>1850476</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1491823</t>
+          <t>1487249</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1552782</t>
+          <t>1547856</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3312996</t>
+          <t>3312636</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3389550</t>
+          <t>3388917</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,14%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14328</t>
+          <t>13650</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34558</t>
+          <t>34379</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38650</t>
+          <t>37864</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69005</t>
+          <t>67332</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57665</t>
+          <t>56607</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>92655</t>
+          <t>91806</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>446623</t>
+          <t>446802</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>466853</t>
+          <t>467531</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>389626</t>
+          <t>391299</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>419981</t>
+          <t>420767</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>847158</t>
+          <t>848007</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>882148</t>
+          <t>883206</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,98%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>276020</t>
+          <t>275302</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>346187</t>
+          <t>345486</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>595054</t>
+          <t>595404</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>693449</t>
+          <t>694710</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>894180</t>
+          <t>896319</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1012924</t>
+          <t>1014387</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3073595</t>
+          <t>3074296</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3143762</t>
+          <t>3144480</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2857571</t>
+          <t>2856310</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2955966</t>
+          <t>2955616</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5957877</t>
+          <t>5956414</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6076621</t>
+          <t>6074482</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,14%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de dolor de espalda en 2016</t>
+          <t>Población con diagnóstico de dolor de espalda, cuello, hombro, cintura (cervical/lumbar) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>82417</t>
+          <t>83832</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>119108</t>
+          <t>118329</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>198660</t>
+          <t>199354</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>252835</t>
+          <t>253794</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>296052</t>
+          <t>291516</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>361501</t>
+          <t>361848</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,69%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>635239</t>
+          <t>636018</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>671930</t>
+          <t>670515</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>741825</t>
+          <t>740866</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>796000</t>
+          <t>795306</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1387506</t>
+          <t>1387159</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1452955</t>
+          <t>1457491</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>83,33%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>120365</t>
+          <t>121807</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>167622</t>
+          <t>168207</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>195081</t>
+          <t>196305</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>254264</t>
+          <t>255903</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>332195</t>
+          <t>332213</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>408744</t>
+          <t>406569</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1908763</t>
+          <t>1908178</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1956020</t>
+          <t>1954578</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1734036</t>
+          <t>1732397</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1793219</t>
+          <t>1791995</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3655941</t>
+          <t>3658116</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3732490</t>
+          <t>3732472</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23577</t>
+          <t>24708</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49523</t>
+          <t>50072</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29147</t>
+          <t>27932</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52560</t>
+          <t>53360</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58171</t>
+          <t>58012</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>94016</t>
+          <t>92301</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>497363</t>
+          <t>496814</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>523309</t>
+          <t>522178</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>496580</t>
+          <t>495780</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>519993</t>
+          <t>521208</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1002011</t>
+          <t>1003726</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1037856</t>
+          <t>1038015</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,71%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>247265</t>
+          <t>246054</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>311520</t>
+          <t>312347</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>445469</t>
+          <t>450052</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>533976</t>
+          <t>536670</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>718158</t>
+          <t>717734</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>827233</t>
+          <t>823117</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,91%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3066098</t>
+          <t>3065271</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3130353</t>
+          <t>3131564</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2998124</t>
+          <t>2995430</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3086631</t>
+          <t>3082048</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6082485</t>
+          <t>6086601</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6191560</t>
+          <t>6191984</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de dolor de espalda en 2023</t>
+          <t>Población con diagnóstico de dolor de espalda, cuello, hombro, cintura (cervical/lumbar) en 2023 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>150784</t>
+          <t>149182</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>187288</t>
+          <t>185657</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>366988</t>
+          <t>364729</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>410795</t>
+          <t>408052</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>526336</t>
+          <t>527234</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>582828</t>
+          <t>584877</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>46,16%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>326654</t>
+          <t>328285</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>363158</t>
+          <t>364760</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>342373</t>
+          <t>345116</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>386180</t>
+          <t>388439</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>684282</t>
+          <t>682233</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>740774</t>
+          <t>739876</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,39%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>232081</t>
+          <t>241270</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>402556</t>
+          <t>399386</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>529851</t>
+          <t>529448</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1149458</t>
+          <t>1058915</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>836880</t>
+          <t>839993</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1637590</t>
+          <t>1576113</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>34,85%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1884032</t>
+          <t>1887202</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2054507</t>
+          <t>2045318</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1086373</t>
+          <t>1176916</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1705980</t>
+          <t>1706383</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2884829</t>
+          <t>2946306</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3685539</t>
+          <t>3682426</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,43%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>67947</t>
+          <t>68632</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>100225</t>
+          <t>102075</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>123135</t>
+          <t>123777</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>158681</t>
+          <t>160035</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>201282</t>
+          <t>200384</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>250559</t>
+          <t>251709</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,28%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>545285</t>
+          <t>543435</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>577563</t>
+          <t>576878</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>501622</t>
+          <t>500268</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>537168</t>
+          <t>536526</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1055254</t>
+          <t>1054104</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1104531</t>
+          <t>1105429</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,65%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>467973</t>
+          <t>464227</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>662066</t>
+          <t>661028</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1067251</t>
+          <t>1061499</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1696588</t>
+          <t>1656049</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1628640</t>
+          <t>1616962</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2434648</t>
+          <t>2419496</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,1%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2783974</t>
+          <t>2785012</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2978067</t>
+          <t>2981813</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1952714</t>
+          <t>1993253</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2582051</t>
+          <t>2587803</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4660694</t>
+          <t>4675846</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5466702</t>
+          <t>5478380</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,21%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1413-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1413-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>238185</t>
+          <t>239158</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>296320</t>
+          <t>293612</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>353518</t>
+          <t>353738</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>421110</t>
+          <t>421179</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>613174</t>
+          <t>607867</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>698151</t>
+          <t>695335</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,63%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>735403</t>
+          <t>738111</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>793538</t>
+          <t>792565</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>894003</t>
+          <t>893934</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>961595</t>
+          <t>961375</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1648684</t>
+          <t>1651500</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1733661</t>
+          <t>1738968</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>74,1%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>176466</t>
+          <t>178568</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>230255</t>
+          <t>233132</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>187482</t>
+          <t>189840</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>243022</t>
+          <t>244840</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>379565</t>
+          <t>380417</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>456087</t>
+          <t>453101</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,81%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1463158</t>
+          <t>1460281</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1516947</t>
+          <t>1514845</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1344651</t>
+          <t>1342833</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1400191</t>
+          <t>1397833</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2824999</t>
+          <t>2827985</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2901521</t>
+          <t>2900669</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,41%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46423</t>
+          <t>46345</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78519</t>
+          <t>75996</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36831</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64787</t>
+          <t>64917</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>89823</t>
+          <t>91664</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>129134</t>
+          <t>130934</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>472889</t>
+          <t>475412</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>504985</t>
+          <t>505063</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>411625</t>
+          <t>411495</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>439581</t>
+          <t>439909</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>898686</t>
+          <t>896886</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>937997</t>
+          <t>936156</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,08%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>491205</t>
+          <t>491274</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>571470</t>
+          <t>578124</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>602194</t>
+          <t>601826</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>692257</t>
+          <t>696772</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1123590</t>
+          <t>1116665</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1242838</t>
+          <t>1239970</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,63%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2705073</t>
+          <t>2698419</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2785338</t>
+          <t>2785269</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2686940</t>
+          <t>2682425</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2777003</t>
+          <t>2777371</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5412903</t>
+          <t>5415771</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5532151</t>
+          <t>5539076</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,22%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>131539</t>
+          <t>131459</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>178781</t>
+          <t>176255</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>332010</t>
+          <t>326785</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>396574</t>
+          <t>393032</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>472309</t>
+          <t>473223</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>555141</t>
+          <t>555505</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,02%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>795862</t>
+          <t>798388</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>843104</t>
+          <t>843184</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>941223</t>
+          <t>944765</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1005787</t>
+          <t>1011012</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1757299</t>
+          <t>1756935</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1840131</t>
+          <t>1839217</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,54%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>113481</t>
+          <t>110846</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>157775</t>
+          <t>158683</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>206736</t>
+          <t>204970</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>267343</t>
+          <t>265538</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>329632</t>
+          <t>328868</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>405913</t>
+          <t>405604</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,91%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1806182</t>
+          <t>1805274</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1850476</t>
+          <t>1853111</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1487249</t>
+          <t>1489054</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1547856</t>
+          <t>1549622</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3312636</t>
+          <t>3312945</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3388917</t>
+          <t>3389681</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,16%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13650</t>
+          <t>14163</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34379</t>
+          <t>34669</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37864</t>
+          <t>37330</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>67332</t>
+          <t>66631</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56607</t>
+          <t>58246</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>91806</t>
+          <t>93116</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>446802</t>
+          <t>446512</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>467531</t>
+          <t>467018</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>391299</t>
+          <t>392000</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>420767</t>
+          <t>421301</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>848007</t>
+          <t>846697</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>883206</t>
+          <t>881567</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,8%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>275302</t>
+          <t>276160</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>345486</t>
+          <t>345150</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>595404</t>
+          <t>598286</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>694710</t>
+          <t>689859</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>896319</t>
+          <t>898016</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1014387</t>
+          <t>1014078</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3074296</t>
+          <t>3074632</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3144480</t>
+          <t>3143622</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2856310</t>
+          <t>2861161</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2955616</t>
+          <t>2952734</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5956414</t>
+          <t>5956723</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6074482</t>
+          <t>6072785</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,12%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>83832</t>
+          <t>83818</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>118329</t>
+          <t>120624</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>199354</t>
+          <t>199087</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>253794</t>
+          <t>255567</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>291516</t>
+          <t>294366</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>361848</t>
+          <t>361212</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>636018</t>
+          <t>633723</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>670515</t>
+          <t>670529</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>740866</t>
+          <t>739093</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>795306</t>
+          <t>795573</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1387159</t>
+          <t>1387795</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1457491</t>
+          <t>1454641</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,17%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>121807</t>
+          <t>122244</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>168207</t>
+          <t>169983</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>196305</t>
+          <t>197664</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>255903</t>
+          <t>257729</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>332213</t>
+          <t>330342</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>406569</t>
+          <t>408182</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1908178</t>
+          <t>1906402</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1954578</t>
+          <t>1954141</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1732397</t>
+          <t>1730571</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1791995</t>
+          <t>1790636</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3658116</t>
+          <t>3656503</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3732472</t>
+          <t>3734343</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,87%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24708</t>
+          <t>23629</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50072</t>
+          <t>49097</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27932</t>
+          <t>28413</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53360</t>
+          <t>52531</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58012</t>
+          <t>57487</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>92301</t>
+          <t>93649</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>496814</t>
+          <t>497789</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>522178</t>
+          <t>523257</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>495780</t>
+          <t>496609</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>521208</t>
+          <t>520727</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1003726</t>
+          <t>1002378</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1038015</t>
+          <t>1038540</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,76%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>246054</t>
+          <t>246584</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>312347</t>
+          <t>310081</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>450052</t>
+          <t>454139</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>536670</t>
+          <t>540449</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>717734</t>
+          <t>714910</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>823117</t>
+          <t>824563</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,93%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3065271</t>
+          <t>3067537</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3131564</t>
+          <t>3131034</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2995430</t>
+          <t>2991651</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3082048</t>
+          <t>3077961</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6086601</t>
+          <t>6085155</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6191984</t>
+          <t>6194808</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,65%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>168494</t>
+          <t>182484</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>149182</t>
+          <t>162036</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>185657</t>
+          <t>203946</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>387639</t>
+          <t>423385</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>364729</t>
+          <t>401730</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>408052</t>
+          <t>445116</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>556133</t>
+          <t>605869</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>527234</t>
+          <t>576049</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>584877</t>
+          <t>637771</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>45,59%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>345448</t>
+          <t>395058</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>328285</t>
+          <t>373596</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>364760</t>
+          <t>415506</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>365529</t>
+          <t>397930</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>345116</t>
+          <t>376199</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>388439</t>
+          <t>419585</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>710977</t>
+          <t>792988</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>682233</t>
+          <t>761086</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>739876</t>
+          <t>822808</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,82%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>753168</t>
+          <t>821315</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>753168</t>
+          <t>821315</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>753168</t>
+          <t>821315</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1267110</t>
+          <t>1398857</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1267110</t>
+          <t>1398857</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1267110</t>
+          <t>1398857</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>345649</t>
+          <t>376094</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>241270</t>
+          <t>341981</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>399386</t>
+          <t>415260</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>703288</t>
+          <t>557216</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>529448</t>
+          <t>521315</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1058915</t>
+          <t>594985</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1048937</t>
+          <t>933310</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>839993</t>
+          <t>880719</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1576113</t>
+          <t>987361</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>22,46%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1940939</t>
+          <t>1850280</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1887202</t>
+          <t>1811114</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2045318</t>
+          <t>1884393</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1532543</t>
+          <t>1612149</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1176916</t>
+          <t>1574380</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1706383</t>
+          <t>1648050</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3473482</t>
+          <t>3462429</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2946306</t>
+          <t>3408378</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3682426</t>
+          <t>3515020</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>79,96%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2286588</t>
+          <t>2226374</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2286588</t>
+          <t>2226374</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2286588</t>
+          <t>2226374</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2235831</t>
+          <t>2169365</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2235831</t>
+          <t>2169365</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2235831</t>
+          <t>2169365</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4522419</t>
+          <t>4395739</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4522419</t>
+          <t>4395739</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4522419</t>
+          <t>4395739</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>83914</t>
+          <t>91426</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68632</t>
+          <t>74839</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>102075</t>
+          <t>109354</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>140926</t>
+          <t>159276</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>123777</t>
+          <t>139367</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>160035</t>
+          <t>179430</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>224840</t>
+          <t>250702</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>200384</t>
+          <t>224304</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>251709</t>
+          <t>278418</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,27%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>561596</t>
+          <t>618977</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>543435</t>
+          <t>601049</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>576878</t>
+          <t>635564</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>519377</t>
+          <t>574919</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>500268</t>
+          <t>554765</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>536526</t>
+          <t>594828</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1080973</t>
+          <t>1193896</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1054104</t>
+          <t>1166180</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1105429</t>
+          <t>1220294</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>84,47%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>645510</t>
+          <t>710403</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>645510</t>
+          <t>710403</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>645510</t>
+          <t>710403</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660303</t>
+          <t>734195</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660303</t>
+          <t>734195</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660303</t>
+          <t>734195</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1305813</t>
+          <t>1444598</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1305813</t>
+          <t>1444598</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1305813</t>
+          <t>1444598</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>598057</t>
+          <t>650004</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>464227</t>
+          <t>605044</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>661028</t>
+          <t>700827</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1231853</t>
+          <t>1139877</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1061499</t>
+          <t>1090834</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1656049</t>
+          <t>1190489</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1829910</t>
+          <t>1789881</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1616962</t>
+          <t>1725807</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2419496</t>
+          <t>1862136</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2847983</t>
+          <t>2864315</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2785012</t>
+          <t>2813492</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2981813</t>
+          <t>2909275</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2417449</t>
+          <t>2584998</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1993253</t>
+          <t>2534386</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2587803</t>
+          <t>2634041</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5265432</t>
+          <t>5449313</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4675846</t>
+          <t>5377058</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5478380</t>
+          <t>5513387</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>76,16%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3446040</t>
+          <t>3514319</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3446040</t>
+          <t>3514319</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3446040</t>
+          <t>3514319</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3649302</t>
+          <t>3724875</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3649302</t>
+          <t>3724875</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3649302</t>
+          <t>3724875</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7095342</t>
+          <t>7239194</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7095342</t>
+          <t>7239194</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7095342</t>
+          <t>7239194</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
